--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260507_205915.xlsx
@@ -4842,7 +4842,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
